--- a/datasets/day1_excel_foundations/06_sorting_filtering_organizing/d1_m6_sorting_answers.xlsx
+++ b/datasets/day1_excel_foundations/06_sorting_filtering_organizing/d1_m6_sorting_answers.xlsx
@@ -552,7 +552,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>4416</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="3">
@@ -588,31 +588,31 @@
         <v>2</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>3332</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O0016</t>
+          <t>O0043</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46107</v>
+        <v>46368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Dell XPS 15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,21 +624,21 @@
         <v>1</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1758</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O0027</t>
+          <t>O0004</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46252</v>
+        <v>46249</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Simbarashe Mutasa</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MacBook Air M4</t>
+          <t>ThinkPad X1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1696</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="6">
@@ -696,26 +696,26 @@
         <v>1</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1663</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O0004</t>
+          <t>O0016</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46249</v>
+        <v>46107</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -732,21 +732,21 @@
         <v>1</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1454.4</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O0043</t>
+          <t>O0018</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46368</v>
+        <v>45508</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tendai Moyo</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dell XPS 15</t>
+          <t>ThinkPad X1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -768,21 +768,21 @@
         <v>1</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1245</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O0018</t>
+          <t>O0019</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45508</v>
+        <v>45671</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -804,26 +804,26 @@
         <v>1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1148</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O0019</t>
+          <t>O0025</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45671</v>
+        <v>46363</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -840,31 +840,31 @@
         <v>1</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>905.25</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O0025</t>
+          <t>O0010</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46363</v>
+        <v>45383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>HP Spectre x360</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -876,31 +876,31 @@
         <v>1</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>882</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O0010</t>
+          <t>O0008</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45383</v>
+        <v>45533</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HP Spectre x360</t>
+          <t>MacBook Air M4</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -912,26 +912,26 @@
         <v>1</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>801.6</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O0008</t>
+          <t>O0027</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45533</v>
+        <v>46252</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -948,7 +948,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>779.2</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14">
@@ -1001,7 +1001,7 @@
         <v>2</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1656</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="16">
@@ -1037,31 +1037,31 @@
         <v>2</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1160</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O0044</t>
+          <t>O0001</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45538</v>
+        <v>46039</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Farai Ncube</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>iPhone 16</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1073,26 +1073,26 @@
         <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>1009.6</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O0001</t>
+          <t>O0045</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46039</v>
+        <v>45494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Amara Otieno</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1115,15 +1115,15 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O0020</t>
+          <t>O0013</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45306</v>
+        <v>45994</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rutendo Chikafu</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1145,31 +1145,31 @@
         <v>1</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>918</v>
+        <v>800</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O0005</t>
+          <t>O0015</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46123</v>
+        <v>46287</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1181,31 +1181,31 @@
         <v>1</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>806</v>
+        <v>800</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O0045</t>
+          <t>O0042</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45494</v>
+        <v>45676</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kagiso Molefe</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>iPhone 16</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1217,21 +1217,21 @@
         <v>1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>782</v>
+        <v>800</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O0013</t>
+          <t>O0044</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45994</v>
+        <v>45538</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1253,21 +1253,21 @@
         <v>1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>724</v>
+        <v>800</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O0042</t>
+          <t>O0005</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45676</v>
+        <v>46123</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tendai Moyo</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>OnePlus 13</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1289,31 +1289,31 @@
         <v>1</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>710</v>
+        <v>600</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>O0015</t>
+          <t>O0020</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46287</v>
+        <v>45306</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>OnePlus 13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1325,7 +1325,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>653.8</v>
+        <v>600</v>
       </c>
     </row>
     <row r="25">
@@ -1378,31 +1378,31 @@
         <v>3</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1806.9</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>O0012</t>
+          <t>O0022</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45857</v>
+        <v>45884</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tendai Moyo</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1414,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1037</v>
+        <v>700</v>
       </c>
     </row>
     <row r="28">
@@ -1450,31 +1450,31 @@
         <v>1</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>889.1</v>
+        <v>700</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>O0022</t>
+          <t>O0009</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45884</v>
+        <v>45856</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>iPad Air 6</t>
+          <t>Surface Go 4</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1486,21 +1486,21 @@
         <v>1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>672.8</v>
+        <v>600</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>O0009</t>
+          <t>O0012</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45856</v>
+        <v>45857</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1522,7 +1522,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>587.2</v>
+        <v>600</v>
       </c>
     </row>
     <row r="31">
@@ -1575,21 +1575,21 @@
         <v>2</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>258.4</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>O0031</t>
+          <t>O0002</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45855</v>
+        <v>45991</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>USB-C Hub 7in1</t>
+          <t>Bluetooth Headphones</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1611,21 +1611,21 @@
         <v>1</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>159</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>O0002</t>
+          <t>O0017</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45991</v>
+        <v>46011</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1647,21 +1647,21 @@
         <v>1</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>119.7</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>O0028</t>
+          <t>O0031</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46162</v>
+        <v>45855</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Laptop Sleeve 15in</t>
+          <t>USB-C Hub 7in1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1683,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>102.2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36">
@@ -1719,21 +1719,21 @@
         <v>1</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>O0017</t>
+          <t>O0028</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46011</v>
+        <v>46162</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tatenda Mpofu</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bluetooth Headphones</t>
+          <t>Laptop Sleeve 15in</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1755,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>56.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
@@ -1778,11 +1778,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>O0023</t>
+          <t>O0007</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45522</v>
+        <v>45458</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Google Nest Hub 3</t>
+          <t>Echo Dot 6</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1805,29 +1805,29 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>619.4</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>O0024</t>
+          <t>O0023</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46343</v>
+        <v>45522</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Farai Ncube</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1844,21 +1844,21 @@
         <v>2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>370</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>O0032</t>
+          <t>O0024</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45776</v>
+        <v>46343</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rutendo Chikafu</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1877,34 +1877,34 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>352</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>O0007</t>
+          <t>O0034</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45458</v>
+        <v>45832</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Google Nest Hub 3</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1913,34 +1913,34 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>326.25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>O0041</t>
+          <t>O0030</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45511</v>
+        <v>46183</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Amara Otieno</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1952,31 +1952,31 @@
         <v>1</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>303.05</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>O0035</t>
+          <t>O0033</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46343</v>
+        <v>46040</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kagiso Molefe</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Google Nest Hub 3</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1988,21 +1988,21 @@
         <v>1</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>289.85</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>O0030</t>
+          <t>O0040</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46183</v>
+        <v>46243</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Simbarashe Mutasa</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2024,26 +2024,26 @@
         <v>1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>263</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>O0034</t>
+          <t>O0032</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45832</v>
+        <v>45776</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Amara Otieno</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2057,34 +2057,34 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>226</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>O0026</t>
+          <t>O0035</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46017</v>
+        <v>46343</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tendai Moyo</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Google Nest Hub 3</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2096,7 +2096,7 @@
         <v>1</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>190.8</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48">
@@ -2132,17 +2132,17 @@
         <v>1</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>177</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>O0033</t>
+          <t>O0026</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46040</v>
+        <v>46017</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ring Doorbell Pro</t>
+          <t>Echo Dot 6</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2168,31 +2168,31 @@
         <v>1</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>148</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>O0040</t>
+          <t>O0041</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46243</v>
+        <v>45511</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Farai Ncube</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ring Doorbell Pro</t>
+          <t>Echo Dot 6</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2204,7 +2204,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>115.9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51">
